--- a/marketing_surveys/016_veterinary_marketing_outreach_survey--marketing_surveys.xlsx
+++ b/marketing_surveys/016_veterinary_marketing_outreach_survey--marketing_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -566,35 +566,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>general_info</t>
+          <t>email_frequency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>General Information</t>
+          <t>How often do you check your emails?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>general_info_3</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>General Information</t>
+          <t>Do you use social media for marketing?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>marketing_channels_2</t>
+          <t>age_range</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What are your marketing channels?</t>
+          <t>What is your age range?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>general_info_2</t>
+          <t>online_advertising</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>General Information</t>
+          <t>Do you prefer online advertising?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>general_info_4</t>
+          <t>experience</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>General Information</t>
+          <t>How many years of experience do you have in the veterinary field?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>marketing_channels_1</t>
+          <t>media_preference</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What are your marketing channels?</t>
+          <t>Do you prefer to receive information through email or print media?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,40 +699,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>general_info_1</t>
+          <t>trade_shows</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>General Information</t>
+          <t>How often do you visit trade shows?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>general_info_3</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>General Information</t>
+          <t>What is your current role in the veterinary industry?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>general_info_2</t>
+          <t>social_media_ads</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>General Information</t>
+          <t>Do you prefer to receive information through social media or online advertising?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,322 +768,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>general_info</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>General Information</t>
+          <t>Do you have any other comments or suggestions?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>general_info_1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>General Information</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>general_info_4</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>General Information</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>general_info_3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>General Information</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>general_info</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>General Information</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>general_info</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>General Information</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>general_info_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>General Information</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>general_info_4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>General Information</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>general_info</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>General Information</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>general_info</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>General Information</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>general_info_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>General Information</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>general_info</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>General Information</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>general_info_1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>General Information</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>general_info_4</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>General Information</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1228,272 +929,340 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>marketing_channels_2_choices</t>
+          <t>social_media_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>marketing_channels_2_choices</t>
+          <t>social_media_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>general_info_2_choices</t>
+          <t>age_range_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>20-29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>20-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>general_info_2_choices</t>
+          <t>age_range_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>30-39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>30-39</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>general_info_4_choices</t>
+          <t>age_range_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>40-49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>40-49</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>general_info_4_choices</t>
+          <t>age_range_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>50-59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>50-59</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>marketing_channels_1_choices</t>
+          <t>age_range_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>60_or_older</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>60 or older</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>marketing_channels_1_choices</t>
+          <t>online_advertising_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>general_info_choices</t>
+          <t>online_advertising_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>general_info_choices</t>
+          <t>media_preference_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>general_info_2_choices</t>
+          <t>media_preference_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>print_media</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Print Media</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>general_info_2_choices</t>
+          <t>trade_shows_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>general_info_choices</t>
+          <t>trade_shows_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>general_info_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>veterinarian</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Veterinarian</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>general_info_3_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>veterinarian_assistant</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Veterinarian Assistant</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>general_info_3_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>pet_owner</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Pet Owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>role_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>industry_representative</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Industry Representative</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>role_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>social_media_ads_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>social_media</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>social_media_ads_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>online_advertising</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Online Advertising</t>
         </is>
       </c>
     </row>
